--- a/docs/lightml/TRACEABILITY_MATRIX.xlsx
+++ b/docs/lightml/TRACEABILITY_MATRIX.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/employment_contract_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/lease_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/software_license_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/service_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/consulting_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/commercial_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/non_disclosure_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/loan_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/partnership_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/purchase_agreement_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>Evidence Not Found</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Detection Specification</t>
+          <t>Detection Specification, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ldv-backend/detector/profiles/it_service_agreement.json</t>
+          <t>ldv-backend/detector/profiles/it_services_agreement.json</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>Evidence Not Found</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Detection Specification</t>
+          <t>Detection Specification, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1797,12 +1797,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>Evidence Not Found</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Detection Specification</t>
+          <t>Detection Specification, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Individual JSON definition, Validation Report Sign-off</t>
+          <t>Individual JSON definition, Legal Evidence</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>docs/lightml/FINAL_PRODUCTION_READINESS_REPORT.md</t>
+          <t>docs/lightml/legal_profile_evidence/general_contract_LEGAL_EVIDENCE.md</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">

--- a/docs/lightml/TRACEABILITY_MATRIX.xlsx
+++ b/docs/lightml/TRACEABILITY_MATRIX.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>docs/lightml/detection_specifications/construction_contract.md</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>docs/lightml/detection_specifications/it_services_contract.md</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Evidence Not Found</t>
+          <t>docs/lightml/detection_specifications/insurance_contract.md</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
